--- a/diseases/d102/2015-2019.xlsx
+++ b/diseases/d102/2015-2019.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>163</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>2.974605898935483</v>
       </c>
@@ -1457,9 +1454,6 @@
       <c r="O6" t="n">
         <v>64</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>1.167943420440926</v>
       </c>
@@ -2001,9 +1995,6 @@
       <c r="O9" t="n">
         <v>54</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0.9854522609970313</v>
       </c>
@@ -2545,9 +2536,6 @@
       <c r="O12" t="n">
         <v>61</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>1.113196072607758</v>
       </c>
@@ -3089,9 +3077,6 @@
       <c r="O15" t="n">
         <v>68</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>1.240939884218484</v>
       </c>
@@ -3633,9 +3618,6 @@
       <c r="O18" t="n">
         <v>87</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>1.587673087161884</v>
       </c>
@@ -4177,9 +4159,6 @@
       <c r="O21" t="n">
         <v>114</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>2.080399217660399</v>
       </c>
@@ -4721,9 +4700,6 @@
       <c r="O24" t="n">
         <v>187</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>3.412584681600831</v>
       </c>
@@ -5265,9 +5241,6 @@
       <c r="O27" t="n">
         <v>151</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>2.75561650760281</v>
       </c>
@@ -5809,9 +5782,6 @@
       <c r="O30" t="n">
         <v>128</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>2.335886840881852</v>
       </c>
@@ -6353,9 +6323,6 @@
       <c r="O33" t="n">
         <v>181</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>3.303089985934494</v>
       </c>
@@ -6897,9 +6864,6 @@
       <c r="O36" t="n">
         <v>205</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>3.741068768599841</v>
       </c>
@@ -7737,9 +7701,6 @@
       <c r="O41" t="n">
         <v>125</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>2.274601130494958</v>
       </c>
@@ -8429,9 +8390,6 @@
       <c r="O45" t="n">
         <v>41</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>0.7460691708023464</v>
       </c>
@@ -9121,9 +9079,6 @@
       <c r="O49" t="n">
         <v>74</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>1.346563869253016</v>
       </c>
@@ -9813,9 +9768,6 @@
       <c r="O53" t="n">
         <v>100</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>1.819680904395967</v>
       </c>
@@ -10505,9 +10457,6 @@
       <c r="O57" t="n">
         <v>127</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>2.310994748582878</v>
       </c>
@@ -11197,9 +11146,6 @@
       <c r="O61" t="n">
         <v>98</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>1.783287286308047</v>
       </c>
@@ -11889,9 +11835,6 @@
       <c r="O65" t="n">
         <v>127</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>2.310994748582878</v>
       </c>
@@ -12581,9 +12524,6 @@
       <c r="O69" t="n">
         <v>195</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>3.548377763572135</v>
       </c>
@@ -13273,9 +13213,6 @@
       <c r="O73" t="n">
         <v>141</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>2.565750075198313</v>
       </c>
@@ -13965,9 +13902,6 @@
       <c r="O77" t="n">
         <v>156</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>2.838702210857709</v>
       </c>
@@ -14657,9 +14591,6 @@
       <c r="O81" t="n">
         <v>246</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>4.476415024814079</v>
       </c>
@@ -15349,9 +15280,6 @@
       <c r="O85" t="n">
         <v>234</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>4.258053316286563</v>
       </c>
@@ -16041,9 +15969,6 @@
       <c r="O89" t="n">
         <v>213</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>3.866824389531907</v>
       </c>
@@ -16585,9 +16510,6 @@
       <c r="O92" t="n">
         <v>148</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>2.686807557045645</v>
       </c>
@@ -17129,9 +17051,6 @@
       <c r="O95" t="n">
         <v>99</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>1.797256406402154</v>
       </c>
@@ -17673,9 +17592,6 @@
       <c r="O98" t="n">
         <v>69</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>1.252633252946956</v>
       </c>
@@ -18217,9 +18133,6 @@
       <c r="O101" t="n">
         <v>89</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>1.615715355250421</v>
       </c>
@@ -18761,9 +18674,6 @@
       <c r="O104" t="n">
         <v>65</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>1.180016832486263</v>
       </c>
@@ -19305,9 +19215,6 @@
       <c r="O107" t="n">
         <v>79</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>1.434174304098689</v>
       </c>
@@ -19849,9 +19756,6 @@
       <c r="O110" t="n">
         <v>132</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>2.396341875202872</v>
       </c>
@@ -20393,9 +20297,6 @@
       <c r="O113" t="n">
         <v>75</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>1.361557883637996</v>
       </c>
@@ -20937,9 +20838,6 @@
       <c r="O116" t="n">
         <v>76</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>1.379711988753169</v>
       </c>
@@ -21481,9 +21379,6 @@
       <c r="O119" t="n">
         <v>112</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>2.033259772899406</v>
       </c>
@@ -22025,9 +21920,6 @@
       <c r="O122" t="n">
         <v>91</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>1.652023565480768</v>
       </c>
@@ -22717,9 +22609,6 @@
       <c r="O126" t="n">
         <v>71</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>1.287226102987334</v>
       </c>
@@ -23261,9 +23150,6 @@
       <c r="O129" t="n">
         <v>26</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="R129" t="n">
         <v>0.4713785729249395</v>
       </c>
@@ -23805,9 +23691,6 @@
       <c r="O132" t="n">
         <v>17</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0.3082090669124604</v>
       </c>
@@ -24349,9 +24232,6 @@
       <c r="O135" t="n">
         <v>17</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="R135" t="n">
         <v>0.3082090669124604</v>
       </c>
@@ -24893,9 +24773,6 @@
       <c r="O138" t="n">
         <v>44</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>0.7977175849498974</v>
       </c>
@@ -25437,9 +25314,6 @@
       <c r="O141" t="n">
         <v>63</v>
       </c>
-      <c r="Q141" t="n">
-        <v>0</v>
-      </c>
       <c r="R141" t="n">
         <v>1.142186542087353</v>
       </c>
@@ -25981,9 +25855,6 @@
       <c r="O144" t="n">
         <v>110</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="R144" t="n">
         <v>1.994293962374744</v>
       </c>
@@ -26525,9 +26396,6 @@
       <c r="O147" t="n">
         <v>119</v>
       </c>
-      <c r="Q147" t="n">
-        <v>0</v>
-      </c>
       <c r="R147" t="n">
         <v>2.157463468387223</v>
       </c>
@@ -27069,9 +26937,6 @@
       <c r="O150" t="n">
         <v>93</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>1.686084895462283</v>
       </c>
@@ -27613,9 +27478,6 @@
       <c r="O153" t="n">
         <v>90</v>
       </c>
-      <c r="Q153" t="n">
-        <v>0</v>
-      </c>
       <c r="R153" t="n">
         <v>1.63169506012479</v>
       </c>
@@ -28157,9 +28019,6 @@
       <c r="O156" t="n">
         <v>149</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>2.701361821762153</v>
       </c>
@@ -28701,9 +28560,6 @@
       <c r="O159" t="n">
         <v>204</v>
       </c>
-      <c r="Q159" t="n">
-        <v>0</v>
-      </c>
       <c r="R159" t="n">
         <v>3.698508802949525</v>
       </c>
@@ -29541,9 +29397,6 @@
       <c r="O164" t="n">
         <v>124</v>
       </c>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
       <c r="R164" t="n">
         <v>2.245661210494699</v>
       </c>
@@ -30233,9 +30086,6 @@
       <c r="O168" t="n">
         <v>50</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>0.9055085526188303</v>
       </c>
@@ -30925,9 +30775,6 @@
       <c r="O172" t="n">
         <v>13</v>
       </c>
-      <c r="Q172" t="n">
-        <v>0</v>
-      </c>
       <c r="R172" t="n">
         <v>0.2354322236808959</v>
       </c>
@@ -31617,9 +31464,6 @@
       <c r="O176" t="n">
         <v>35</v>
       </c>
-      <c r="Q176" t="n">
-        <v>0</v>
-      </c>
       <c r="R176" t="n">
         <v>0.6338559868331812</v>
       </c>
@@ -32309,9 +32153,6 @@
       <c r="O180" t="n">
         <v>56</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>1.01416957893309</v>
       </c>
@@ -33001,9 +32842,6 @@
       <c r="O184" t="n">
         <v>66</v>
       </c>
-      <c r="Q184" t="n">
-        <v>0</v>
-      </c>
       <c r="R184" t="n">
         <v>1.195271289456856</v>
       </c>
@@ -33693,9 +33531,6 @@
       <c r="O188" t="n">
         <v>92</v>
       </c>
-      <c r="Q188" t="n">
-        <v>0</v>
-      </c>
       <c r="R188" t="n">
         <v>1.666135736818648</v>
       </c>
@@ -34385,9 +34220,6 @@
       <c r="O192" t="n">
         <v>171</v>
       </c>
-      <c r="Q192" t="n">
-        <v>0</v>
-      </c>
       <c r="R192" t="n">
         <v>3.0968392499564</v>
       </c>
@@ -35077,9 +34909,6 @@
       <c r="O196" t="n">
         <v>123</v>
       </c>
-      <c r="Q196" t="n">
-        <v>0</v>
-      </c>
       <c r="R196" t="n">
         <v>2.227551039442323</v>
       </c>
@@ -35769,9 +35598,6 @@
       <c r="O200" t="n">
         <v>117</v>
       </c>
-      <c r="Q200" t="n">
-        <v>0</v>
-      </c>
       <c r="R200" t="n">
         <v>2.118890013128063</v>
       </c>
@@ -36461,9 +36287,6 @@
       <c r="O204" t="n">
         <v>195</v>
       </c>
-      <c r="Q204" t="n">
-        <v>0</v>
-      </c>
       <c r="R204" t="n">
         <v>3.531483355213438</v>
       </c>
@@ -37152,9 +36975,6 @@
       </c>
       <c r="O208" t="n">
         <v>214</v>
-      </c>
-      <c r="Q208" t="n">
-        <v>0</v>
       </c>
       <c r="R208" t="n">
         <v>3.875576605208594</v>
